--- a/问题4/灵敏度分析_数据扰动.xlsx
+++ b/问题4/灵敏度分析_数据扰动.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>被剔点替换为该日'附件1 形状×日因子'的结构值</t>
+          <t>被剔点替换为该日'附件1 形状×日因子'的结构值；零差异为结构性结论：9 个点全部落在光伏富余、计划购电量 x=0 且充电已顶功率上限的时段，抬价不改变任何决策（单日核验见运行日志）</t>
         </is>
       </c>
     </row>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>11535436.8889</v>
+        <v>12813701.2091</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>-9.988099999999999</v>
+        <v>-0.0137</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>13005664.1955</v>
+        <v>14448325.5765</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>-9.995900000000001</v>
+        <v>-0.0122</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>277412.2151</v>
+        <v>308344.1774</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
